--- a/测试用例/.cli_smoke/job77_bill.xlsx
+++ b/测试用例/.cli_smoke/job77_bill.xlsx
@@ -3310,7 +3310,7 @@
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="35" t="n">
-        <v>102165.0</v>
+        <v>102269.5</v>
       </c>
       <c r="L10" s="24"/>
     </row>
@@ -38527,10 +38527,10 @@
         <v>1.0</v>
       </c>
       <c r="J1184" s="23" t="n">
-        <v>27.5</v>
+        <v>132.0</v>
       </c>
       <c r="K1184" s="23" t="n">
-        <v>27.5</v>
+        <v>132.0</v>
       </c>
       <c r="L1184" s="24"/>
     </row>
